--- a/file/Microsoft_Forms_Web_VPATJ09240.xlsx
+++ b/file/Microsoft_Forms_Web_VPATJ09240.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9C3DFA4C-5E95-4312-9B2D-2D9998E37515}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{479881BA-50D6-4629-A1D4-8D05B85A3AFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{1B19E273-EFEF-497C-8733-F5F5F4BDB342}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{A32A8C0A-5081-44AF-9366-43AA638AA6E0}"/>
   </bookViews>
   <sheets>
-    <sheet name="情報アクセシビリティ自己評価様式" sheetId="1" r:id="rId1"/>
-    <sheet name="様式作成時の技術基準" sheetId="2" r:id="rId2"/>
+    <sheet name="情報アクセシビリティ自己評価様式" sheetId="2" r:id="rId1"/>
+    <sheet name="様式作成時の技術基準" sheetId="3" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">様式作成時の技術基準!$A$1:$M$90</definedName>
@@ -30,844 +30,226 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="2"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
+  <metadataTypes count="1">
+    <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLRICHVALUE" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <valueMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </valueMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="235">
-  <si>
-    <r>
-      <t>ICT</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>機器・サービスのアクセシビリティ自己評価様式</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>作成日：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>2025</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>年</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>11</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>月</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>25</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>日</t>
-    </r>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>製品画像</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>企業・団体名</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>日本マイクロソフト株式会社</t>
-    </r>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="225">
+  <si>
+    <t>ICT機器・サービスのアクセシビリティ自己評価様式</t>
+  </si>
+  <si>
+    <t>作成日：2026年10月16日</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>製品画像</t>
+  </si>
+  <si>
+    <t>企業・団体名</t>
+  </si>
+  <si>
+    <t>日本マイクロソフト株式会社</t>
     <rPh sb="0" eb="2">
       <t>ニホン</t>
     </rPh>
     <rPh sb="9" eb="13">
       <t>カブシキガイシャ</t>
     </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>Microsoft Forms
-(Web)</t>
-  </si>
-  <si>
-    <r>
-      <t>ICT</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>機器・サービス名称</t>
-    </r>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>ICT機器・サービス名称</t>
   </si>
   <si>
     <t>Microsoft Forms(Web)</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>型番</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>ICT</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>機器・サービス概要</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Microsoft Forms(Web)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>は、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>M365</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>と連携し、アンケートや投票・クイズで手軽にデータとフィードバックを収集・分析して意思決定を支援する</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Web</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>アプリです。</t>
-    </r>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>問合せ先</t>
-    </r>
+  </si>
+  <si>
+    <t>型番</t>
+  </si>
+  <si>
+    <t>ICT機器・サービス概要</t>
+  </si>
+  <si>
+    <t>Microsoft Forms(Web)は、M365と連携し、アンケートや投票・クイズで手軽にデータとフィードバックを収集・分析して意思決定を支援するWebアプリです。</t>
+  </si>
+  <si>
+    <t>問合せ先</t>
   </si>
   <si>
     <t>0120-167-400</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>ウェブサイト</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>URL</t>
-    </r>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>ウェブサイトURL</t>
   </si>
   <si>
     <t>https://forms.office.com/</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>機能性能</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>配慮対象アクセス</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>評価結果</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>概要</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>視力なしでの使用（全盲）</t>
-    </r>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>対応している</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>すべての製品において要件を満たす。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>製品・サービスが視覚的な操作モードで提供される場合、視力を必要としない操作モードが用意されているか</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>限られた視力での使用（弱視、ロービジョン）</t>
-    </r>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>製品・サービスが視覚的な操作モードで提供される場合、限られた視力で対応可能な操作モードが用意されているか</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>色知覚なしでの使用</t>
-    </r>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>評価不要</t>
-    </r>
+  </si>
+  <si>
+    <t>機能性能</t>
+  </si>
+  <si>
+    <t>配慮対象アクセス</t>
+  </si>
+  <si>
+    <t>評価結果</t>
+  </si>
+  <si>
+    <t>概要</t>
+  </si>
+  <si>
+    <t>視力なしでの使用（全盲）</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>対応している</t>
+  </si>
+  <si>
+    <t>すべての製品において要件を満たす。</t>
+  </si>
+  <si>
+    <t>製品・サービスが視覚的な操作モードで提供される場合、視力を必要としない操作モードが用意されているか</t>
+  </si>
+  <si>
+    <t>限られた視力での使用（弱視、ロービジョン）</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>製品・サービスが視覚的な操作モードで提供される場合、限られた視力で対応可能な操作モードが用意されているか</t>
+  </si>
+  <si>
+    <t>色知覚なしでの使用</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>評価不要</t>
     <rPh sb="0" eb="4">
       <t>ヒョウカフヨウ</t>
     </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>米国リハビリテーション法</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>508</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>条を用いているため評価の対象外である。</t>
-    </r>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>製品・サービスが視覚的な操作モードで提供される場合、色知覚を必要としない操作モードが用意されているか</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>聴力なしでの使用（全ろう）</t>
-    </r>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>製品・サービスが聴覚的な操作モードで提供される場合、聴力を必要としない操作モードが用意されているか</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>限られた聴力での使用（難聴）</t>
-    </r>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>製品・サービスが聴覚的な操作モードで行われる場合、強化された音声機能によって限られた聴力を補う操作モードが提供されているか</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>発話能力なしでの使用</t>
-    </r>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>対応している</t>
-    </r>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>米国リハビリテーション法508条を用いているため評価の対象外である。</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>製品・サービスが視覚的な操作モードで提供される場合、色知覚を必要としない操作モードが用意されているか</t>
+  </si>
+  <si>
+    <t>聴力なしでの使用（全ろう）</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>製品・サービスが聴覚的な操作モードで提供される場合、聴力を必要としない操作モードが用意されているか</t>
+  </si>
+  <si>
+    <t>限られた聴力での使用（難聴）</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>製品・サービスが聴覚的な操作モードで行われる場合、強化された音声機能によって限られた聴力を補う操作モードが提供されているか</t>
+  </si>
+  <si>
+    <t>発話能力なしでの使用</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>対応している</t>
     <rPh sb="0" eb="2">
       <t>タイオウ</t>
     </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>すべての製品において要件を満たす。</t>
-    </r>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>製品・サービスが発話による操作モードで行われる場合、音声入力を必要としない操作モードが用意されているか</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>限られた器用さ又は力での使用</t>
-    </r>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>製品・サービスが手の動作を必要とする場合、細かい運動制御等を必要としない操作モードが用意されているか</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>限られた手の届く範囲での使用</t>
-    </r>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>製品・サービスが手動による操作モードで提供される場合、手の届く範囲で、かつ限られた力で対応可能な操作モードが用意されているか</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>光の点滅による影響の最小化（光感受性発作）</t>
-    </r>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>対応している</t>
-    </r>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>すべての製品において要件を満たす。</t>
-    </r>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>すべての製品において要件を満たす。</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>製品・サービスが発話による操作モードで行われる場合、音声入力を必要としない操作モードが用意されているか</t>
+  </si>
+  <si>
+    <t>限られた器用さ又は力での使用</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>製品・サービスが手の動作を必要とする場合、細かい運動制御等を必要としない操作モードが用意されているか</t>
+  </si>
+  <si>
+    <t>限られた手の届く範囲での使用</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>製品・サービスが手動による操作モードで提供される場合、手の届く範囲で、かつ限られた力で対応可能な操作モードが用意されているか</t>
+  </si>
+  <si>
+    <t>光の点滅による影響の最小化（光感受性発作）</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>対応している</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>すべての製品において要件を満たす。</t>
     <rPh sb="4" eb="6">
       <t>セイヒン</t>
     </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>製品が視覚的な操作モードで提供される場合、光感受性発作を引き起こすリスクを最小化するような配慮がなされているか</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>プライバシー</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>製品・サービスがアクセシビリティ機能を提供する場合、アクセシビリティ機能を使用するにあたりプライバシーが守られる操作モードが用意されているか</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>サポート対応　概要</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>ドキュメントとサポートサービス</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>製品の取扱説明書や問合せ先が提供されているか。また、アクセシビリティに配慮したサポート（取扱説明書、電話や手話（筆記）窓口、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>FAX</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>等）が提供されているか。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>用いた技術基準</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>米国リハビリテーション法</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>508</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>条</t>
-    </r>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>免責事項</t>
-    </r>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>製品が視覚的な操作モードで提供される場合、光感受性発作を引き起こすリスクを最小化するような配慮がなされているか</t>
+  </si>
+  <si>
+    <t>プライバシー</t>
+  </si>
+  <si>
+    <t>製品・サービスがアクセシビリティ機能を提供する場合、アクセシビリティ機能を使用するにあたりプライバシーが守られる操作モードが用意されているか</t>
+  </si>
+  <si>
+    <t>サポート対応　概要</t>
+  </si>
+  <si>
+    <t>ドキュメントとサポートサービス</t>
+  </si>
+  <si>
+    <t>製品の取扱説明書や問合せ先が提供されているか。また、アクセシビリティに配慮したサポート（取扱説明書、電話や手話（筆記）窓口、FAX等）が提供されているか。</t>
+  </si>
+  <si>
+    <t>用いた技術基準</t>
+  </si>
+  <si>
+    <t>米国リハビリテーション法508条</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>免責事項</t>
   </si>
   <si>
     <t>章・項・節</t>
@@ -880,18 +262,18 @@
     <rPh sb="4" eb="5">
       <t>セツ</t>
     </rPh>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>Provision Title</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>項目名</t>
     <rPh sb="0" eb="3">
       <t>コウモクメイ</t>
     </rPh>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>規格内容</t>
@@ -901,84 +283,48 @@
     <rPh sb="2" eb="4">
       <t>ナイヨウ</t>
     </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>視力なしでの使用（全盲）</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>限られた視力での使用（弱視、ロービジョン）</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>色知覚なしでの使用</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>聴力なしでの使用（全ろう）</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>限られた聴力での使用（難聴）</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>発話能力なしでの使用</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>限られた器用さ又は力での使用</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>限られた手の届く範囲での使用</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>光の点滅による影響の最小化（光感受性発作）</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>General</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>一般</t>
     <rPh sb="0" eb="2">
       <t>イッパン</t>
     </rPh>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>●</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>Functional Performance Criteria</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>機能的性能基準</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>Without Vision</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>視力なし</t>
     <rPh sb="0" eb="2">
       <t>シリョク</t>
     </rPh>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>●</t>
   </si>
   <si>
     <t>With Limited Vision</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>限られた視力</t>
@@ -988,11 +334,11 @@
     <rPh sb="4" eb="6">
       <t>シリョク</t>
     </rPh>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>Without Perception of Color</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>色彩感覚なし</t>
@@ -1002,22 +348,22 @@
     <rPh sb="2" eb="4">
       <t>カンカク</t>
     </rPh>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t xml:space="preserve"> Without Hearing</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>聴力なし</t>
     <rPh sb="0" eb="2">
       <t>チョウリョク</t>
     </rPh>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>With Limited Hearing</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>限られた聴力</t>
@@ -1027,22 +373,22 @@
     <rPh sb="4" eb="6">
       <t>チョウリョク</t>
     </rPh>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>Without Speech</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>発話能力なし</t>
     <rPh sb="0" eb="4">
       <t>ハツワノウリョク</t>
     </rPh>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t xml:space="preserve"> With Limited Manipulation</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>限定的な操作</t>
@@ -1052,11 +398,11 @@
     <rPh sb="4" eb="6">
       <t>ソウサ</t>
     </rPh>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t xml:space="preserve"> With Limited Reach and Strength</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>限られた手の届く範囲と力の強さ</t>
@@ -1066,138 +412,138 @@
     <rPh sb="13" eb="14">
       <t>ツヨ</t>
     </rPh>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t xml:space="preserve"> With Limited Language, Cognitive, and Learning Abilities</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>限られた言語能力、認知能力、学習能力</t>
     <rPh sb="0" eb="1">
       <t>カギ</t>
     </rPh>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>Closed Functionality</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>クローズドな機能</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>Speech-Output Enabled</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>音声出力可能</t>
   </si>
   <si>
     <t>402.2.1</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t xml:space="preserve"> Information Displayed On-Screen</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t xml:space="preserve"> 画面に表示される情報</t>
   </si>
   <si>
     <t>402.2.2</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>Transactional Outputs</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>トランザクション出力</t>
   </si>
   <si>
     <t>402.2.3</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>Speech Delivery Type and Coordination</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>音声配信の種類と連携</t>
   </si>
   <si>
     <t>402.2.4</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>User Control</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>ユーザーコントロール</t>
   </si>
   <si>
     <t>402.2.5</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>Braille Instructions</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t xml:space="preserve"> 点字説明</t>
   </si>
   <si>
     <t>Volume</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>音量</t>
   </si>
   <si>
     <t>402.3.1</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>Private Listening</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>個人的な聞き取り</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>402.3.2</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>Non-Private Listening</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>非個人的な聞き取り</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t xml:space="preserve">Characters on Display Screens
 </t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>ディスプレイ上の文字</t>
   </si>
   <si>
     <t>Characters on Variable Message Signs</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>可変メッセージ看板の文字</t>
   </si>
   <si>
     <t>Biometrics</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>バイオメトリクス</t>
@@ -1210,88 +556,88 @@
   </si>
   <si>
     <t>Preservation of Information Provided for Accessibility</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>アクセシビリティのための情報の保存</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>一般</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>Privacy</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>個人情報保護</t>
   </si>
   <si>
     <t>Standard Connections</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>標準接続</t>
   </si>
   <si>
     <t>Operable Parts</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>操作可能な部品</t>
   </si>
   <si>
     <t xml:space="preserve"> Contrast</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t xml:space="preserve"> コントラスト</t>
   </si>
   <si>
     <t xml:space="preserve"> Input Controls (and sub-provisions)</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t xml:space="preserve"> 入力コントロール（およびその下位規定）</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t xml:space="preserve"> Key Repeat</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>キーリピート</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>Timed Response</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>時限反応</t>
   </si>
   <si>
     <t>Operation</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>操作方法</t>
   </si>
   <si>
     <t xml:space="preserve"> Keys, Tickets, and Fare Cards</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t xml:space="preserve"> キー、チケット、料金カード</t>
     <rPh sb="9" eb="11">
       <t>リョウキン</t>
     </rPh>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>Reach Height (and sub-provisions)</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>届く高さ（およびその下位規定）</t>
@@ -1301,32 +647,32 @@
     <rPh sb="2" eb="3">
       <t>タカ</t>
     </rPh>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>Display Screens</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>表示画面</t>
   </si>
   <si>
     <t>Visibility</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>視認性</t>
   </si>
   <si>
     <t>Flashing</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>点滅表示</t>
   </si>
   <si>
     <t>Status Indicators</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>状態表示</t>
@@ -1336,88 +682,88 @@
     <rPh sb="2" eb="4">
       <t>ヒョウジ</t>
     </rPh>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>Color Coding</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>カラーコード</t>
   </si>
   <si>
     <t>Audible Signals</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>可聴信号</t>
   </si>
   <si>
     <t>ICT With Two-Way Voice Communication</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>双方向音声通話機能付きICT</t>
   </si>
   <si>
     <t xml:space="preserve"> Volume Gain</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t xml:space="preserve"> ボリュームゲイン</t>
   </si>
   <si>
     <t>Interference Reduction and Magnetic Coupling (and sub-provisions)</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>妨害波低減と磁気結合（およびその下位規定）</t>
   </si>
   <si>
     <t>Digitally Encoded Speech</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>デジタル符号化音声</t>
   </si>
   <si>
     <t xml:space="preserve"> Real-Time Text Functionality (Reserved)</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t xml:space="preserve"> リアルタイムテキスト機能(予約)</t>
   </si>
   <si>
     <t xml:space="preserve"> Caller ID</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t xml:space="preserve"> 発信者番号通知</t>
   </si>
   <si>
     <t>Video Communication</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>ビデオ通信</t>
   </si>
   <si>
     <t>Caption Processing Technologies</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>キャプション処理技術</t>
   </si>
   <si>
     <t>General (includes sub-provisions)</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>一般（下位規定含む）</t>
   </si>
   <si>
     <t>Audio Description Processing Technology</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>音声説明処理技術</t>
@@ -1427,28 +773,28 @@
   </si>
   <si>
     <t>User Controls for Captions and Audio Description</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>字幕・音声説明のユーザー制御技術</t>
   </si>
   <si>
     <t>General (and sub-provisions)</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>一般（および下位規定）</t>
   </si>
   <si>
     <t>Interoperability With Assistive Technology</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>支援技術との相互運用性</t>
   </si>
   <si>
     <t>Accessibility Services (and sub-provisions)</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>アクセシビリティサービス（および下位規定）</t>
@@ -1458,164 +804,164 @@
   </si>
   <si>
     <t>Platform Accessibility Features</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>プラットフォームアクセシビリティ機能</t>
   </si>
   <si>
     <t>A. Section 9.3.3</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>Enable sequential entry of multiple (chorded) keystrokes</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>複数のキーストロークを連続して入力できる</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>B. Section 9.3.4</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>Provide adjustment of delay before key acceptance</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>キー受理までの遅延時間の調整</t>
   </si>
   <si>
     <t>C. Section 9.3.5</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>Provide adjustment of same-key double-strike acceptance</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>同じキーの連打を受け入れるかどうかを調整できるようにした</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>D. Section 10.6.7</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>Allow users to choose visual alternative for audio output</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>音声出力に代わる視覚的な選択肢をユーザーが選択可能</t>
   </si>
   <si>
     <t>E. Section 10.6.8</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t xml:space="preserve"> Synchronize audio equivalents for visual events</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t xml:space="preserve"> 視覚的イベントと音声を同期させる</t>
   </si>
   <si>
     <t>F. Section 10.6.9</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>Provide speech output services</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>音声出力サービスの提供</t>
   </si>
   <si>
     <t>G. Section 10.7.1</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>Display any captions provided</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>提供されたキャプションの表示</t>
   </si>
   <si>
     <t>Applications</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>アプリケーション</t>
   </si>
   <si>
     <t xml:space="preserve"> User Preferences</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t xml:space="preserve"> ユーザー設定</t>
   </si>
   <si>
     <t>Alternative User Interfaces</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>代替ユーザーインターフェイス</t>
   </si>
   <si>
     <t>User Controls for Captions and Audio Description (includes sub-provisions)</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>キャプションとオーディオディスクリプションのためのユーザーコントロール（下位規定を含む）</t>
   </si>
   <si>
     <t>Authoring Tools</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>オーサリングツール</t>
   </si>
   <si>
     <t xml:space="preserve"> Content Creation or Editing</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t xml:space="preserve"> コンテンツの作成または編集</t>
   </si>
   <si>
     <t>504.2.1</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>Preservation of Information Provided for Accessibility in Format Conversion</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>フォーマット変換におけるアクセシビリティのための情報提供の保存</t>
   </si>
   <si>
     <t>504.2.2</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>PDF Export</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>PDFの書き出し</t>
   </si>
   <si>
     <t>Prompts</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>プロンプト</t>
   </si>
   <si>
     <t>Templates</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>テンプレート</t>
@@ -1625,7 +971,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1647,13 +993,6 @@
       <b/>
       <sz val="14"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14"/>
-      <color rgb="FF000000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <family val="3"/>
       <charset val="128"/>
@@ -1666,26 +1005,13 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="10.5"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
-      <sz val="10.5"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10.5"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <family val="3"/>
@@ -1695,13 +1021,28 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
     </font>
     <font>
       <b/>
+      <sz val="28"/>
+      <color rgb="FF000000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FF000000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="ＭＳ Ｐゴシック"/>
       <family val="3"/>
       <charset val="128"/>
@@ -1715,35 +1056,18 @@
       <charset val="128"/>
     </font>
     <font>
-      <b/>
-      <sz val="28"/>
+      <sz val="10.5"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10.5"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10.5"/>
       <name val="ＭＳ Ｐゴシック"/>
       <family val="3"/>
       <charset val="128"/>
     </font>
     <font>
-      <u/>
-      <sz val="10.5"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10.5"/>
+      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
     </font>
     <font>
       <b/>
@@ -2080,184 +1404,184 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -2281,16 +1605,16 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2309,6 +1633,72 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
+<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
+  <global>
+    <keyFlags>
+      <key name="_Self">
+        <flag name="ExcludeFromFile" value="1"/>
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_DisplayString">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Flags">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Format">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_SubLabel">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Attribution">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Icon">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Display">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_CanonicalPropertyNames">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_ClassificationId">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+    </keyFlags>
+  </global>
+</rvTypesInfo>
+</file>
+
+<file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
+  <rv s="0">
+    <v>0</v>
+    <v>5</v>
+    <v>Formsのロゴ画像</v>
+  </rv>
+</rvData>
+</file>
+
+<file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
+  <s t="_localImage">
+    <k n="_rvRel:LocalImageIdentifier" t="i"/>
+    <k n="CalcOrigin" t="i"/>
+    <k n="Text" t="s"/>
+  </s>
+</rvStructures>
+</file>
+
+<file path=xl/richData/richValueRel.xml><?xml version="1.0" encoding="utf-8"?>
+<richValueRels xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/richvaluerel" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <rel r:id="rId1"/>
+</richValueRels>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2627,242 +2017,242 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAB43FD9-D50E-4A72-B07E-B81CCA73A568}">
-  <sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65776905-B7E2-47D8-AB18-99BD2A2D208F}">
+  <sheetPr codeName="Sheet298">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:I54"/>
   <sheetFormatPr defaultColWidth="8.58203125" defaultRowHeight="14.5" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="20.08203125" style="3" customWidth="1"/>
-    <col min="2" max="2" width="13.08203125" style="3" customWidth="1"/>
-    <col min="3" max="3" width="10.33203125" style="3" customWidth="1"/>
-    <col min="4" max="4" width="18.58203125" style="3" customWidth="1"/>
-    <col min="5" max="7" width="9.08203125" style="3" customWidth="1"/>
-    <col min="8" max="8" width="8.58203125" style="3"/>
-    <col min="9" max="9" width="28.33203125" style="3" customWidth="1"/>
-    <col min="10" max="16384" width="8.58203125" style="3"/>
+    <col min="1" max="1" width="20.08203125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="13.08203125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="10.33203125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="18.58203125" style="2" customWidth="1"/>
+    <col min="5" max="7" width="9.08203125" style="2" customWidth="1"/>
+    <col min="8" max="8" width="8.58203125" style="2"/>
+    <col min="9" max="9" width="28.33203125" style="2" customWidth="1"/>
+    <col min="10" max="16384" width="8.58203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:9" ht="16.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="4"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="5"/>
-      <c r="B3" s="5"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="6" t="s">
+      <c r="A3" s="4"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="11" t="s">
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="10" t="e" vm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="H4" s="11"/>
+      <c r="I4" s="12"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="13"/>
+      <c r="B5" s="14"/>
+      <c r="C5" s="15"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="15"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="16"/>
+      <c r="H5" s="17"/>
+      <c r="I5" s="18"/>
+    </row>
+    <row r="6" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="12"/>
-      <c r="I4" s="13"/>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="14"/>
-      <c r="B5" s="15"/>
-      <c r="C5" s="16"/>
-      <c r="D5" s="16"/>
-      <c r="E5" s="16"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="17"/>
-      <c r="H5" s="18"/>
-      <c r="I5" s="19"/>
-    </row>
-    <row r="6" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="7" t="s">
+      <c r="B6" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="16"/>
+      <c r="H6" s="17"/>
+      <c r="I6" s="18"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="13"/>
+      <c r="B7" s="14"/>
+      <c r="C7" s="15"/>
+      <c r="D7" s="15"/>
+      <c r="E7" s="15"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="16"/>
+      <c r="H7" s="17"/>
+      <c r="I7" s="18"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="5"/>
-      <c r="G6" s="17"/>
-      <c r="H6" s="18"/>
-      <c r="I6" s="19"/>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="14"/>
-      <c r="B7" s="15"/>
-      <c r="C7" s="16"/>
-      <c r="D7" s="16"/>
-      <c r="E7" s="16"/>
-      <c r="F7" s="5"/>
-      <c r="G7" s="17"/>
-      <c r="H7" s="18"/>
-      <c r="I7" s="19"/>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="7" t="s">
+      <c r="B8" s="7"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="9"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="17"/>
+      <c r="I8" s="18"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="13"/>
+      <c r="B9" s="14"/>
+      <c r="C9" s="15"/>
+      <c r="D9" s="15"/>
+      <c r="E9" s="15"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="16"/>
+      <c r="H9" s="17"/>
+      <c r="I9" s="18"/>
+    </row>
+    <row r="10" spans="1:9" ht="54" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="8"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="10"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="17"/>
-      <c r="H8" s="18"/>
-      <c r="I8" s="19"/>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="14"/>
-      <c r="B9" s="15"/>
-      <c r="C9" s="16"/>
-      <c r="D9" s="16"/>
-      <c r="E9" s="16"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="17"/>
-      <c r="H9" s="18"/>
-      <c r="I9" s="19"/>
-    </row>
-    <row r="10" spans="1:9" ht="54" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="7" t="s">
+      <c r="B10" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="20" t="s">
+      <c r="C10" s="20"/>
+      <c r="D10" s="20"/>
+      <c r="E10" s="21"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="16"/>
+      <c r="H10" s="17"/>
+      <c r="I10" s="18"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" s="13"/>
+      <c r="B11" s="14"/>
+      <c r="C11" s="15"/>
+      <c r="D11" s="15"/>
+      <c r="E11" s="15"/>
+      <c r="F11" s="4"/>
+      <c r="G11" s="16"/>
+      <c r="H11" s="17"/>
+      <c r="I11" s="18"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="21"/>
-      <c r="D10" s="21"/>
-      <c r="E10" s="22"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="17"/>
-      <c r="H10" s="18"/>
-      <c r="I10" s="19"/>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="14"/>
-      <c r="B11" s="15"/>
-      <c r="C11" s="16"/>
-      <c r="D11" s="16"/>
-      <c r="E11" s="16"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="17"/>
-      <c r="H11" s="18"/>
-      <c r="I11" s="19"/>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="7" t="s">
+      <c r="B12" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="9"/>
+      <c r="F12" s="4"/>
+      <c r="G12" s="16"/>
+      <c r="H12" s="17"/>
+      <c r="I12" s="18"/>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" s="13"/>
+      <c r="B13" s="14"/>
+      <c r="C13" s="15"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="4"/>
+      <c r="G13" s="16"/>
+      <c r="H13" s="17"/>
+      <c r="I13" s="18"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="10"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="17"/>
-      <c r="H12" s="18"/>
-      <c r="I12" s="19"/>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="14"/>
-      <c r="B13" s="15"/>
-      <c r="C13" s="16"/>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="17"/>
-      <c r="H13" s="18"/>
-      <c r="I13" s="19"/>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="7" t="s">
+      <c r="B14" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="23" t="s">
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="9"/>
+      <c r="F14" s="4"/>
+      <c r="G14" s="23"/>
+      <c r="H14" s="24"/>
+      <c r="I14" s="25"/>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" s="4"/>
+      <c r="B15" s="4"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4"/>
+      <c r="I15" s="4"/>
+    </row>
+    <row r="16" spans="1:9" ht="16.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="24"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="25"/>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="5"/>
-      <c r="B15" s="5"/>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
-      <c r="H15" s="5"/>
-      <c r="I15" s="5"/>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="26" t="s">
-        <v>15</v>
-      </c>
-      <c r="B16" s="5"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
-      <c r="G16" s="5"/>
-      <c r="H16" s="5"/>
-      <c r="I16" s="5"/>
+      <c r="B16" s="4"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
+      <c r="I16" s="4"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="27" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B17" s="28"/>
       <c r="C17" s="29"/>
       <c r="D17" s="30" t="s">
+        <v>16</v>
+      </c>
+      <c r="E17" s="31" t="s">
         <v>17</v>
-      </c>
-      <c r="E17" s="31" t="s">
-        <v>18</v>
       </c>
       <c r="F17" s="31"/>
       <c r="G17" s="31"/>
@@ -2871,15 +2261,15 @@
     </row>
     <row r="18" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="32" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B18" s="33"/>
       <c r="C18" s="34"/>
       <c r="D18" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="E18" s="36" t="s">
         <v>20</v>
-      </c>
-      <c r="E18" s="36" t="s">
-        <v>21</v>
       </c>
       <c r="F18" s="37"/>
       <c r="G18" s="37"/>
@@ -2888,7 +2278,7 @@
     </row>
     <row r="19" spans="1:9" ht="50.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="39" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B19" s="40"/>
       <c r="C19" s="41"/>
@@ -2901,15 +2291,15 @@
     </row>
     <row r="20" spans="1:9" ht="25.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="32" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B20" s="33"/>
       <c r="C20" s="34"/>
       <c r="D20" s="46" t="s">
+        <v>19</v>
+      </c>
+      <c r="E20" s="36" t="s">
         <v>20</v>
-      </c>
-      <c r="E20" s="36" t="s">
-        <v>21</v>
       </c>
       <c r="F20" s="37"/>
       <c r="G20" s="37"/>
@@ -2918,7 +2308,7 @@
     </row>
     <row r="21" spans="1:9" ht="44.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="39" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B21" s="40"/>
       <c r="C21" s="41"/>
@@ -2931,15 +2321,15 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="32" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B22" s="33"/>
       <c r="C22" s="34"/>
       <c r="D22" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="E22" s="42" t="s">
         <v>26</v>
-      </c>
-      <c r="E22" s="42" t="s">
-        <v>27</v>
       </c>
       <c r="F22" s="42"/>
       <c r="G22" s="42"/>
@@ -2948,7 +2338,7 @@
     </row>
     <row r="23" spans="1:9" ht="51.65" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="39" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B23" s="40"/>
       <c r="C23" s="41"/>
@@ -2961,15 +2351,15 @@
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="32" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B24" s="33"/>
       <c r="C24" s="34"/>
       <c r="D24" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="E24" s="36" t="s">
         <v>20</v>
-      </c>
-      <c r="E24" s="36" t="s">
-        <v>21</v>
       </c>
       <c r="F24" s="37"/>
       <c r="G24" s="37"/>
@@ -2978,7 +2368,7 @@
     </row>
     <row r="25" spans="1:9" ht="51" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="39" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B25" s="40"/>
       <c r="C25" s="41"/>
@@ -2991,15 +2381,15 @@
     </row>
     <row r="26" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="32" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B26" s="33"/>
       <c r="C26" s="34"/>
       <c r="D26" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="E26" s="36" t="s">
         <v>20</v>
-      </c>
-      <c r="E26" s="36" t="s">
-        <v>21</v>
       </c>
       <c r="F26" s="37"/>
       <c r="G26" s="37"/>
@@ -3008,7 +2398,7 @@
     </row>
     <row r="27" spans="1:9" ht="51.65" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="39" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B27" s="40"/>
       <c r="C27" s="41"/>
@@ -3021,15 +2411,15 @@
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="32" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B28" s="33"/>
       <c r="C28" s="34"/>
       <c r="D28" s="46" t="s">
+        <v>33</v>
+      </c>
+      <c r="E28" s="42" t="s">
         <v>34</v>
-      </c>
-      <c r="E28" s="42" t="s">
-        <v>35</v>
       </c>
       <c r="F28" s="42"/>
       <c r="G28" s="42"/>
@@ -3038,7 +2428,7 @@
     </row>
     <row r="29" spans="1:9" ht="51.65" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="39" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B29" s="40"/>
       <c r="C29" s="41"/>
@@ -3051,15 +2441,15 @@
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="32" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B30" s="33"/>
       <c r="C30" s="34"/>
       <c r="D30" s="46" t="s">
+        <v>19</v>
+      </c>
+      <c r="E30" s="36" t="s">
         <v>20</v>
-      </c>
-      <c r="E30" s="36" t="s">
-        <v>21</v>
       </c>
       <c r="F30" s="37"/>
       <c r="G30" s="37"/>
@@ -3068,7 +2458,7 @@
     </row>
     <row r="31" spans="1:9" ht="51.65" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="39" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B31" s="40"/>
       <c r="C31" s="41"/>
@@ -3081,7 +2471,7 @@
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="32" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B32" s="33"/>
       <c r="C32" s="34"/>
@@ -3094,7 +2484,7 @@
     </row>
     <row r="33" spans="1:9" ht="69.650000000000006" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="39" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B33" s="40"/>
       <c r="C33" s="41"/>
@@ -3107,15 +2497,15 @@
     </row>
     <row r="34" spans="1:9" ht="25.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="32" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B34" s="33"/>
       <c r="C34" s="34"/>
       <c r="D34" s="42" t="s">
+        <v>41</v>
+      </c>
+      <c r="E34" s="42" t="s">
         <v>42</v>
-      </c>
-      <c r="E34" s="42" t="s">
-        <v>43</v>
       </c>
       <c r="F34" s="42"/>
       <c r="G34" s="42"/>
@@ -3124,7 +2514,7 @@
     </row>
     <row r="35" spans="1:9" ht="51.65" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="39" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B35" s="40"/>
       <c r="C35" s="41"/>
@@ -3148,15 +2538,15 @@
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="27" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B37" s="28"/>
       <c r="C37" s="29"/>
       <c r="D37" s="30" t="s">
+        <v>16</v>
+      </c>
+      <c r="E37" s="31" t="s">
         <v>17</v>
-      </c>
-      <c r="E37" s="31" t="s">
-        <v>18</v>
       </c>
       <c r="F37" s="31"/>
       <c r="G37" s="31"/>
@@ -3165,15 +2555,15 @@
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="32" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B38" s="33"/>
       <c r="C38" s="34"/>
       <c r="D38" s="42" t="s">
+        <v>41</v>
+      </c>
+      <c r="E38" s="42" t="s">
         <v>42</v>
-      </c>
-      <c r="E38" s="42" t="s">
-        <v>43</v>
       </c>
       <c r="F38" s="42"/>
       <c r="G38" s="42"/>
@@ -3182,7 +2572,7 @@
     </row>
     <row r="39" spans="1:9" ht="64.400000000000006" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="39" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B39" s="40"/>
       <c r="C39" s="41"/>
@@ -3194,40 +2584,40 @@
       <c r="I39" s="42"/>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A40" s="5"/>
-      <c r="B40" s="5"/>
-      <c r="C40" s="5"/>
-      <c r="D40" s="5"/>
-      <c r="E40" s="5"/>
-      <c r="F40" s="5"/>
-      <c r="G40" s="5"/>
-      <c r="H40" s="5"/>
-      <c r="I40" s="5"/>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A40" s="4"/>
+      <c r="B40" s="4"/>
+      <c r="C40" s="4"/>
+      <c r="D40" s="4"/>
+      <c r="E40" s="4"/>
+      <c r="F40" s="4"/>
+      <c r="G40" s="4"/>
+      <c r="H40" s="4"/>
+      <c r="I40" s="4"/>
+    </row>
+    <row r="41" spans="1:9" ht="16.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" s="26" t="s">
-        <v>47</v>
-      </c>
-      <c r="B41" s="5"/>
-      <c r="C41" s="5"/>
-      <c r="D41" s="5"/>
-      <c r="E41" s="5"/>
-      <c r="F41" s="5"/>
-      <c r="G41" s="5"/>
-      <c r="H41" s="5"/>
-      <c r="I41" s="5"/>
+        <v>46</v>
+      </c>
+      <c r="B41" s="4"/>
+      <c r="C41" s="4"/>
+      <c r="D41" s="4"/>
+      <c r="E41" s="4"/>
+      <c r="F41" s="4"/>
+      <c r="G41" s="4"/>
+      <c r="H41" s="4"/>
+      <c r="I41" s="4"/>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" s="27" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B42" s="28"/>
       <c r="C42" s="29"/>
       <c r="D42" s="30" t="s">
+        <v>16</v>
+      </c>
+      <c r="E42" s="31" t="s">
         <v>17</v>
-      </c>
-      <c r="E42" s="31" t="s">
-        <v>18</v>
       </c>
       <c r="F42" s="31"/>
       <c r="G42" s="31"/>
@@ -3236,15 +2626,15 @@
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" s="32" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B43" s="33"/>
       <c r="C43" s="34"/>
       <c r="D43" s="42" t="s">
+        <v>41</v>
+      </c>
+      <c r="E43" s="42" t="s">
         <v>42</v>
-      </c>
-      <c r="E43" s="42" t="s">
-        <v>43</v>
       </c>
       <c r="F43" s="42"/>
       <c r="G43" s="42"/>
@@ -3253,7 +2643,7 @@
     </row>
     <row r="44" spans="1:9" ht="52.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" s="39" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B44" s="40"/>
       <c r="C44" s="41"/>
@@ -3265,22 +2655,22 @@
       <c r="I44" s="42"/>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A45" s="5"/>
-      <c r="B45" s="5"/>
-      <c r="C45" s="5"/>
-      <c r="D45" s="5"/>
-      <c r="E45" s="5"/>
-      <c r="F45" s="5"/>
-      <c r="G45" s="5"/>
-      <c r="H45" s="5"/>
-      <c r="I45" s="5"/>
+      <c r="A45" s="4"/>
+      <c r="B45" s="4"/>
+      <c r="C45" s="4"/>
+      <c r="D45" s="4"/>
+      <c r="E45" s="4"/>
+      <c r="F45" s="4"/>
+      <c r="G45" s="4"/>
+      <c r="H45" s="4"/>
+      <c r="I45" s="4"/>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" s="54" t="s">
+        <v>49</v>
+      </c>
+      <c r="B46" s="42" t="s">
         <v>50</v>
-      </c>
-      <c r="B46" s="42" t="s">
-        <v>51</v>
       </c>
       <c r="C46" s="42"/>
       <c r="D46" s="42"/>
@@ -3292,18 +2682,18 @@
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" s="55"/>
-      <c r="B47" s="15"/>
-      <c r="C47" s="16"/>
-      <c r="D47" s="16"/>
-      <c r="E47" s="16"/>
-      <c r="F47" s="5"/>
+      <c r="B47" s="14"/>
+      <c r="C47" s="15"/>
+      <c r="D47" s="15"/>
+      <c r="E47" s="15"/>
+      <c r="F47" s="4"/>
       <c r="G47" s="56"/>
       <c r="H47" s="56"/>
       <c r="I47" s="57"/>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" s="54" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B48" s="42"/>
       <c r="C48" s="42"/>
@@ -3441,9 +2831,9 @@
     <mergeCell ref="B12:E12"/>
     <mergeCell ref="B14:E14"/>
   </mergeCells>
-  <phoneticPr fontId="4"/>
+  <phoneticPr fontId="3"/>
   <hyperlinks>
-    <hyperlink ref="B14" r:id="rId1" xr:uid="{89EA7608-B880-4ACA-A7E7-9FE50AD7FCC5}"/>
+    <hyperlink ref="B14" r:id="rId1" xr:uid="{CDE04B5E-0CA3-475A-85F1-A13EDE413D98}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="25" orientation="portrait" r:id="rId2"/>
@@ -3451,7 +2841,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97803549-921E-4482-BDE4-96A9F0A40378}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81B7E9DA-5634-4608-845A-EB4D40C50C9F}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:M90"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
@@ -3464,43 +2854,43 @@
   <sheetData>
     <row r="1" spans="1:13" ht="71.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1" s="59" t="s">
+        <v>52</v>
+      </c>
+      <c r="B1" s="60" t="s">
         <v>53</v>
       </c>
-      <c r="B1" s="60" t="s">
+      <c r="C1" s="60" t="s">
         <v>54</v>
       </c>
-      <c r="C1" s="60" t="s">
+      <c r="D1" s="61" t="s">
         <v>55</v>
       </c>
-      <c r="D1" s="61" t="s">
-        <v>56</v>
-      </c>
       <c r="E1" s="60" t="s">
-        <v>57</v>
+        <v>18</v>
       </c>
       <c r="F1" s="60" t="s">
-        <v>58</v>
+        <v>22</v>
       </c>
       <c r="G1" s="60" t="s">
-        <v>59</v>
+        <v>24</v>
       </c>
       <c r="H1" s="60" t="s">
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="I1" s="60" t="s">
-        <v>61</v>
+        <v>30</v>
       </c>
       <c r="J1" s="60" t="s">
-        <v>62</v>
+        <v>32</v>
       </c>
       <c r="K1" s="60" t="s">
-        <v>63</v>
+        <v>36</v>
       </c>
       <c r="L1" s="60" t="s">
-        <v>64</v>
+        <v>38</v>
       </c>
       <c r="M1" s="60" t="s">
-        <v>65</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -3508,36 +2898,36 @@
         <v>301</v>
       </c>
       <c r="B2" s="63" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="C2" s="64" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="D2" s="65"/>
       <c r="E2" s="66" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="F2" s="66" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="G2" s="67"/>
       <c r="H2" s="66" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="I2" s="66" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="J2" s="66" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="K2" s="66" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="L2" s="66" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="M2" s="66" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -3545,10 +2935,10 @@
         <v>302</v>
       </c>
       <c r="B3" s="63" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="C3" s="64" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="D3" s="65"/>
       <c r="E3" s="66"/>
@@ -3566,14 +2956,14 @@
         <v>302.10000000000002</v>
       </c>
       <c r="B4" s="64" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="C4" s="64" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="D4" s="65"/>
       <c r="E4" s="65" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="F4" s="65"/>
       <c r="G4" s="68"/>
@@ -3589,15 +2979,15 @@
         <v>302.2</v>
       </c>
       <c r="B5" s="64" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="C5" s="64" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="D5" s="65"/>
       <c r="E5" s="65"/>
       <c r="F5" s="65" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="G5" s="68"/>
       <c r="H5" s="65"/>
@@ -3612,15 +3002,15 @@
         <v>302.3</v>
       </c>
       <c r="B6" s="64" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="C6" s="64" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="D6" s="65"/>
       <c r="E6" s="65"/>
       <c r="F6" s="65" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="G6" s="68"/>
       <c r="H6" s="65"/>
@@ -3635,17 +3025,17 @@
         <v>302.39999999999998</v>
       </c>
       <c r="B7" s="64" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="C7" s="64" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="D7" s="65"/>
       <c r="E7" s="65"/>
       <c r="F7" s="65"/>
       <c r="G7" s="68"/>
       <c r="H7" s="65" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="I7" s="65"/>
       <c r="J7" s="65"/>
@@ -3658,10 +3048,10 @@
         <v>302.5</v>
       </c>
       <c r="B8" s="64" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="C8" s="64" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="D8" s="65"/>
       <c r="E8" s="65"/>
@@ -3669,7 +3059,7 @@
       <c r="G8" s="68"/>
       <c r="H8" s="65"/>
       <c r="I8" s="65" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="J8" s="65"/>
       <c r="K8" s="65"/>
@@ -3681,10 +3071,10 @@
         <v>302.60000000000002</v>
       </c>
       <c r="B9" s="64" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="C9" s="64" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="D9" s="65"/>
       <c r="E9" s="65"/>
@@ -3693,7 +3083,7 @@
       <c r="H9" s="65"/>
       <c r="I9" s="65"/>
       <c r="J9" s="65" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="K9" s="65"/>
       <c r="L9" s="65"/>
@@ -3704,10 +3094,10 @@
         <v>302.7</v>
       </c>
       <c r="B10" s="64" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="C10" s="64" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="D10" s="65"/>
       <c r="E10" s="65"/>
@@ -3717,10 +3107,10 @@
       <c r="I10" s="65"/>
       <c r="J10" s="65"/>
       <c r="K10" s="65" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="L10" s="65" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="M10" s="65"/>
     </row>
@@ -3729,10 +3119,10 @@
         <v>302.8</v>
       </c>
       <c r="B11" s="64" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="C11" s="64" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="D11" s="65"/>
       <c r="E11" s="65"/>
@@ -3742,10 +3132,10 @@
       <c r="I11" s="65"/>
       <c r="J11" s="65"/>
       <c r="K11" s="65" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="L11" s="65" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="M11" s="65"/>
     </row>
@@ -3754,10 +3144,10 @@
         <v>302.89999999999998</v>
       </c>
       <c r="B12" s="64" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="C12" s="64" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="D12" s="65"/>
       <c r="E12" s="65"/>
@@ -3775,17 +3165,17 @@
         <v>402</v>
       </c>
       <c r="B13" s="64" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="C13" s="64" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="D13" s="65"/>
       <c r="E13" s="66" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="F13" s="66" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="G13" s="67"/>
       <c r="H13" s="66"/>
@@ -3800,10 +3190,10 @@
         <v>402.1</v>
       </c>
       <c r="B14" s="70" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="C14" s="70" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="D14" s="71"/>
       <c r="E14" s="66"/>
@@ -3821,10 +3211,10 @@
         <v>402.2</v>
       </c>
       <c r="B15" s="64" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="C15" s="64" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="D15" s="65"/>
       <c r="E15" s="66"/>
@@ -3839,17 +3229,17 @@
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="65" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="B16" s="64" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="C16" s="64" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="D16" s="65"/>
       <c r="E16" s="65" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="F16" s="65"/>
       <c r="G16" s="68"/>
@@ -3862,17 +3252,17 @@
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="65" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="B17" s="64" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="C17" s="64" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="D17" s="65"/>
       <c r="E17" s="65" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="F17" s="65"/>
       <c r="G17" s="68"/>
@@ -3885,20 +3275,20 @@
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="65" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="B18" s="64" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="C18" s="64" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="D18" s="65"/>
       <c r="E18" s="65" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="F18" s="65" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="G18" s="68"/>
       <c r="H18" s="65"/>
@@ -3910,20 +3300,20 @@
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="65" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="B19" s="64" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="C19" s="64" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="D19" s="65"/>
       <c r="E19" s="65" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="F19" s="65" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="G19" s="68"/>
       <c r="H19" s="65"/>
@@ -3935,17 +3325,17 @@
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="65" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="B20" s="64" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="C20" s="64" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="D20" s="65"/>
       <c r="E20" s="65" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="F20" s="65"/>
       <c r="G20" s="68"/>
@@ -3961,10 +3351,10 @@
         <v>402.3</v>
       </c>
       <c r="B21" s="64" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="C21" s="64" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="D21" s="65"/>
       <c r="E21" s="65"/>
@@ -3972,7 +3362,7 @@
       <c r="G21" s="68"/>
       <c r="H21" s="65"/>
       <c r="I21" s="65" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="J21" s="65"/>
       <c r="K21" s="65"/>
@@ -3981,23 +3371,23 @@
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="65" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="B22" s="64" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="C22" s="64" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="D22" s="65"/>
       <c r="E22" s="65" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="F22" s="65"/>
       <c r="G22" s="68"/>
       <c r="H22" s="65"/>
       <c r="I22" s="65" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="J22" s="65"/>
       <c r="K22" s="65"/>
@@ -4006,23 +3396,23 @@
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="65" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="B23" s="64" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="C23" s="64" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="D23" s="65"/>
       <c r="E23" s="65" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="F23" s="65"/>
       <c r="G23" s="68"/>
       <c r="H23" s="65"/>
       <c r="I23" s="65" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="J23" s="65"/>
       <c r="K23" s="65"/>
@@ -4034,15 +3424,15 @@
         <v>402.4</v>
       </c>
       <c r="B24" s="64" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="C24" s="64" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="D24" s="65"/>
       <c r="E24" s="65"/>
       <c r="F24" s="65" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="G24" s="68"/>
       <c r="H24" s="65"/>
@@ -4057,15 +3447,15 @@
         <v>402.5</v>
       </c>
       <c r="B25" s="64" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="C25" s="64" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="D25" s="65"/>
       <c r="E25" s="65"/>
       <c r="F25" s="65" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="G25" s="68"/>
       <c r="H25" s="65"/>
@@ -4080,27 +3470,27 @@
         <v>403</v>
       </c>
       <c r="B26" s="64" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="C26" s="64" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="D26" s="65"/>
       <c r="E26" s="66"/>
       <c r="F26" s="66" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="G26" s="67"/>
       <c r="H26" s="66"/>
       <c r="I26" s="66"/>
       <c r="J26" s="66" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="K26" s="66" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="L26" s="66" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="M26" s="66"/>
     </row>
@@ -4109,10 +3499,10 @@
         <v>403.1</v>
       </c>
       <c r="B27" s="64" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="C27" s="64" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="D27" s="65"/>
       <c r="E27" s="66"/>
@@ -4130,29 +3520,29 @@
         <v>404</v>
       </c>
       <c r="B28" s="64" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="C28" s="64" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="D28" s="65"/>
       <c r="E28" s="66" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="F28" s="66"/>
       <c r="G28" s="67"/>
       <c r="H28" s="66" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="I28" s="66" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="J28" s="66"/>
       <c r="K28" s="66" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="L28" s="66" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="M28" s="66"/>
     </row>
@@ -4161,10 +3551,10 @@
         <v>404.1</v>
       </c>
       <c r="B29" s="64" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="C29" s="64" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="D29" s="65"/>
       <c r="E29" s="66"/>
@@ -4182,17 +3572,17 @@
         <v>405</v>
       </c>
       <c r="B30" s="64" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="C30" s="64" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="D30" s="65"/>
       <c r="E30" s="66" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="F30" s="66" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="G30" s="67"/>
       <c r="H30" s="66"/>
@@ -4207,10 +3597,10 @@
         <v>405.1</v>
       </c>
       <c r="B31" s="64" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="C31" s="64" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="D31" s="65"/>
       <c r="E31" s="66"/>
@@ -4228,30 +3618,30 @@
         <v>406</v>
       </c>
       <c r="B32" s="64" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="C32" s="64" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="D32" s="65"/>
       <c r="E32" s="66" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="F32" s="66"/>
       <c r="G32" s="67"/>
       <c r="H32" s="66"/>
       <c r="I32" s="66" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="J32" s="66"/>
       <c r="K32" s="66" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="L32" s="66" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="M32" s="66" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -4259,10 +3649,10 @@
         <v>406.1</v>
       </c>
       <c r="B33" s="64" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="C33" s="64" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="D33" s="65"/>
       <c r="E33" s="66"/>
@@ -4280,31 +3670,31 @@
         <v>407</v>
       </c>
       <c r="B34" s="64" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="C34" s="64" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="D34" s="65"/>
       <c r="E34" s="66" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="F34" s="66" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="G34" s="67"/>
       <c r="H34" s="66" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="I34" s="66" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="J34" s="66"/>
       <c r="K34" s="66" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="L34" s="66" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="M34" s="66"/>
     </row>
@@ -4313,10 +3703,10 @@
         <v>407.1</v>
       </c>
       <c r="B35" s="64" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="C35" s="64" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="D35" s="65"/>
       <c r="E35" s="66"/>
@@ -4334,15 +3724,15 @@
         <v>407.2</v>
       </c>
       <c r="B36" s="64" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="C36" s="64" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="D36" s="65"/>
       <c r="E36" s="65"/>
       <c r="F36" s="65" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="G36" s="68"/>
       <c r="H36" s="65"/>
@@ -4357,14 +3747,14 @@
         <v>407.3</v>
       </c>
       <c r="B37" s="64" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="C37" s="64" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="D37" s="65"/>
       <c r="E37" s="65" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="F37" s="65"/>
       <c r="G37" s="68"/>
@@ -4380,10 +3770,10 @@
         <v>407.4</v>
       </c>
       <c r="B38" s="64" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="C38" s="64" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="D38" s="65"/>
       <c r="E38" s="65"/>
@@ -4393,10 +3783,10 @@
       <c r="I38" s="65"/>
       <c r="J38" s="65"/>
       <c r="K38" s="65" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="L38" s="65" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="M38" s="65"/>
     </row>
@@ -4405,27 +3795,27 @@
         <v>407.5</v>
       </c>
       <c r="B39" s="64" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="C39" s="64" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="D39" s="65"/>
       <c r="E39" s="65" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="F39" s="65" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="G39" s="68"/>
       <c r="H39" s="65"/>
       <c r="I39" s="65"/>
       <c r="J39" s="65"/>
       <c r="K39" s="65" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="L39" s="65" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="M39" s="65"/>
     </row>
@@ -4434,10 +3824,10 @@
         <v>407.6</v>
       </c>
       <c r="B40" s="64" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="C40" s="64" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="D40" s="65"/>
       <c r="E40" s="65"/>
@@ -4447,10 +3837,10 @@
       <c r="I40" s="65"/>
       <c r="J40" s="65"/>
       <c r="K40" s="65" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="L40" s="65" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="M40" s="65"/>
     </row>
@@ -4459,14 +3849,14 @@
         <v>407.7</v>
       </c>
       <c r="B41" s="64" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="C41" s="64" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="D41" s="65"/>
       <c r="E41" s="65" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="F41" s="65"/>
       <c r="G41" s="68"/>
@@ -4482,10 +3872,10 @@
         <v>407.8</v>
       </c>
       <c r="B42" s="64" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="C42" s="64" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="D42" s="65"/>
       <c r="E42" s="65"/>
@@ -4495,10 +3885,10 @@
       <c r="I42" s="65"/>
       <c r="J42" s="65"/>
       <c r="K42" s="65" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="L42" s="65" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="M42" s="65"/>
     </row>
@@ -4507,10 +3897,10 @@
         <v>408</v>
       </c>
       <c r="B43" s="64" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="C43" s="64" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="D43" s="66"/>
       <c r="E43" s="66"/>
@@ -4520,10 +3910,10 @@
       <c r="I43" s="66"/>
       <c r="J43" s="66"/>
       <c r="K43" s="66" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="L43" s="66" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="M43" s="66"/>
     </row>
@@ -4532,10 +3922,10 @@
         <v>408.1</v>
       </c>
       <c r="B44" s="64" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="C44" s="64" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="D44" s="66"/>
       <c r="E44" s="66"/>
@@ -4553,10 +3943,10 @@
         <v>408.2</v>
       </c>
       <c r="B45" s="64" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="C45" s="64" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="D45" s="66"/>
       <c r="E45" s="66"/>
@@ -4574,10 +3964,10 @@
         <v>408.3</v>
       </c>
       <c r="B46" s="64" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="C46" s="64" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="D46" s="65"/>
       <c r="E46" s="65"/>
@@ -4595,14 +3985,14 @@
         <v>409</v>
       </c>
       <c r="B47" s="64" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="C47" s="64" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="D47" s="65"/>
       <c r="E47" s="66" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="F47" s="66"/>
       <c r="G47" s="67"/>
@@ -4618,10 +4008,10 @@
         <v>409.1</v>
       </c>
       <c r="B48" s="64" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="C48" s="64" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="D48" s="65"/>
       <c r="E48" s="66"/>
@@ -4639,15 +4029,15 @@
         <v>410</v>
       </c>
       <c r="B49" s="64" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="C49" s="64" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="D49" s="65"/>
       <c r="E49" s="66"/>
       <c r="F49" s="66" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="G49" s="67"/>
       <c r="H49" s="66"/>
@@ -4662,10 +4052,10 @@
         <v>410.1</v>
       </c>
       <c r="B50" s="64" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="C50" s="64" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="D50" s="65"/>
       <c r="E50" s="66"/>
@@ -4683,20 +4073,20 @@
         <v>411</v>
       </c>
       <c r="B51" s="64" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="C51" s="64" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="D51" s="65"/>
       <c r="E51" s="66"/>
       <c r="F51" s="66"/>
       <c r="G51" s="67"/>
       <c r="H51" s="66" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="I51" s="66" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="J51" s="66"/>
       <c r="K51" s="66"/>
@@ -4708,10 +4098,10 @@
         <v>411.1</v>
       </c>
       <c r="B52" s="64" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="C52" s="64" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="D52" s="65"/>
       <c r="E52" s="66"/>
@@ -4729,29 +4119,29 @@
         <v>412</v>
       </c>
       <c r="B53" s="64" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="C53" s="64" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="D53" s="65"/>
       <c r="E53" s="66" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="F53" s="66"/>
       <c r="G53" s="67"/>
       <c r="H53" s="66" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="I53" s="66" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="J53" s="66"/>
       <c r="K53" s="66" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="L53" s="66" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="M53" s="66"/>
     </row>
@@ -4760,10 +4150,10 @@
         <v>412.1</v>
       </c>
       <c r="B54" s="64" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="C54" s="64" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="D54" s="65"/>
       <c r="E54" s="66"/>
@@ -4781,10 +4171,10 @@
         <v>412.2</v>
       </c>
       <c r="B55" s="64" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="C55" s="64" t="s">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="D55" s="65"/>
       <c r="E55" s="65"/>
@@ -4792,7 +4182,7 @@
       <c r="G55" s="68"/>
       <c r="H55" s="65"/>
       <c r="I55" s="65" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="J55" s="65"/>
       <c r="K55" s="65"/>
@@ -4804,10 +4194,10 @@
         <v>412.3</v>
       </c>
       <c r="B56" s="64" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="C56" s="64" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="D56" s="65"/>
       <c r="E56" s="65"/>
@@ -4815,7 +4205,7 @@
       <c r="G56" s="68"/>
       <c r="H56" s="65"/>
       <c r="I56" s="65" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="J56" s="65"/>
       <c r="K56" s="65"/>
@@ -4827,10 +4217,10 @@
         <v>412.4</v>
       </c>
       <c r="B57" s="64" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="C57" s="64" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="D57" s="65"/>
       <c r="E57" s="65"/>
@@ -4838,7 +4228,7 @@
       <c r="G57" s="68"/>
       <c r="H57" s="65"/>
       <c r="I57" s="65" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="J57" s="65"/>
       <c r="K57" s="65"/>
@@ -4850,10 +4240,10 @@
         <v>412.5</v>
       </c>
       <c r="B58" s="64" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="C58" s="64" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="D58" s="65"/>
       <c r="E58" s="65"/>
@@ -4871,24 +4261,24 @@
         <v>412.6</v>
       </c>
       <c r="B59" s="64" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="C59" s="64" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="D59" s="65"/>
       <c r="E59" s="65" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="F59" s="65" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="G59" s="68"/>
       <c r="H59" s="65" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="I59" s="65" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="J59" s="65"/>
       <c r="K59" s="65"/>
@@ -4900,17 +4290,17 @@
         <v>412.7</v>
       </c>
       <c r="B60" s="64" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="C60" s="64" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="D60" s="65"/>
       <c r="E60" s="65"/>
       <c r="F60" s="65"/>
       <c r="G60" s="68"/>
       <c r="H60" s="65" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="I60" s="65"/>
       <c r="J60" s="65"/>
@@ -4923,20 +4313,20 @@
         <v>413</v>
       </c>
       <c r="B61" s="64" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="C61" s="64" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="D61" s="65"/>
       <c r="E61" s="66"/>
       <c r="F61" s="66"/>
       <c r="G61" s="67"/>
       <c r="H61" s="66" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="I61" s="66" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="J61" s="66"/>
       <c r="K61" s="66"/>
@@ -4948,10 +4338,10 @@
         <v>411.1</v>
       </c>
       <c r="B62" s="64" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="C62" s="64" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="D62" s="65"/>
       <c r="E62" s="66"/>
@@ -4969,14 +4359,14 @@
         <v>414</v>
       </c>
       <c r="B63" s="64" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="C63" s="64" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="D63" s="65"/>
       <c r="E63" s="66" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="F63" s="66"/>
       <c r="G63" s="67"/>
@@ -4992,10 +4382,10 @@
         <v>412.1</v>
       </c>
       <c r="B64" s="64" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="C64" s="64" t="s">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="D64" s="65"/>
       <c r="E64" s="66"/>
@@ -5013,22 +4403,22 @@
         <v>415</v>
       </c>
       <c r="B65" s="64" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="C65" s="64" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="D65" s="65"/>
       <c r="E65" s="66" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="F65" s="66"/>
       <c r="G65" s="67"/>
       <c r="H65" s="66" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="I65" s="66" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="J65" s="66"/>
       <c r="K65" s="66"/>
@@ -5040,10 +4430,10 @@
         <v>413.1</v>
       </c>
       <c r="B66" s="64" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="C66" s="64" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="D66" s="65"/>
       <c r="E66" s="66"/>
@@ -5061,31 +4451,31 @@
         <v>502</v>
       </c>
       <c r="B67" s="64" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="C67" s="64" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="D67" s="65"/>
       <c r="E67" s="66" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="F67" s="66" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="G67" s="67"/>
       <c r="H67" s="66" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="I67" s="66" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="J67" s="66"/>
       <c r="K67" s="66" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="L67" s="66" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="M67" s="66"/>
     </row>
@@ -5094,10 +4484,10 @@
         <v>502.1</v>
       </c>
       <c r="B68" s="64" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="C68" s="64" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="D68" s="65"/>
       <c r="E68" s="66"/>
@@ -5115,29 +4505,29 @@
         <v>502.2</v>
       </c>
       <c r="B69" s="64" t="s">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="C69" s="64" t="s">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="D69" s="65"/>
       <c r="E69" s="65" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="F69" s="65"/>
       <c r="G69" s="68"/>
       <c r="H69" s="65" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="I69" s="65" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="J69" s="65"/>
       <c r="K69" s="65" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="L69" s="65" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="M69" s="65"/>
     </row>
@@ -5146,14 +4536,14 @@
         <v>502.3</v>
       </c>
       <c r="B70" s="64" t="s">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="C70" s="64" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="D70" s="65"/>
       <c r="E70" s="65" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="F70" s="65"/>
       <c r="G70" s="68"/>
@@ -5161,10 +4551,10 @@
       <c r="I70" s="65"/>
       <c r="J70" s="65"/>
       <c r="K70" s="65" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="L70" s="65" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="M70" s="65"/>
     </row>
@@ -5173,43 +4563,43 @@
         <v>502.4</v>
       </c>
       <c r="B71" s="64" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="C71" s="64" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="D71" s="65"/>
       <c r="E71" s="65" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="F71" s="65" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="G71" s="68"/>
       <c r="H71" s="65" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="I71" s="65" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="J71" s="65"/>
       <c r="K71" s="65" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="L71" s="65" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="M71" s="65"/>
     </row>
     <row r="72" spans="1:13" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A72" s="65" t="s">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="B72" s="64" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="C72" s="64" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="D72" s="65"/>
       <c r="E72" s="65"/>
@@ -5219,22 +4609,22 @@
       <c r="I72" s="65"/>
       <c r="J72" s="65"/>
       <c r="K72" s="65" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="L72" s="65" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="M72" s="65"/>
     </row>
     <row r="73" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A73" s="65" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="B73" s="64" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="C73" s="64" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="D73" s="65"/>
       <c r="E73" s="65"/>
@@ -5244,22 +4634,22 @@
       <c r="I73" s="65"/>
       <c r="J73" s="65"/>
       <c r="K73" s="65" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="L73" s="65" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="M73" s="65"/>
     </row>
     <row r="74" spans="1:13" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A74" s="65" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="B74" s="64" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="C74" s="64" t="s">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="D74" s="65"/>
       <c r="E74" s="65"/>
@@ -5269,32 +4659,32 @@
       <c r="I74" s="65"/>
       <c r="J74" s="65"/>
       <c r="K74" s="65" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="L74" s="65" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="M74" s="65"/>
     </row>
     <row r="75" spans="1:13" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A75" s="65" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="B75" s="64" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="C75" s="64" t="s">
-        <v>203</v>
+        <v>193</v>
       </c>
       <c r="D75" s="65"/>
       <c r="E75" s="65"/>
       <c r="F75" s="65"/>
       <c r="G75" s="68"/>
       <c r="H75" s="65" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="I75" s="65" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="J75" s="65"/>
       <c r="K75" s="65"/>
@@ -5303,23 +4693,23 @@
     </row>
     <row r="76" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A76" s="65" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="B76" s="64" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="C76" s="64" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="D76" s="65"/>
       <c r="E76" s="65"/>
       <c r="F76" s="65" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="G76" s="68"/>
       <c r="H76" s="65"/>
       <c r="I76" s="65" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="J76" s="65"/>
       <c r="K76" s="65"/>
@@ -5328,26 +4718,26 @@
     </row>
     <row r="77" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A77" s="65" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="B77" s="64" t="s">
-        <v>208</v>
+        <v>198</v>
       </c>
       <c r="C77" s="64" t="s">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="D77" s="65"/>
       <c r="E77" s="65" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="F77" s="65" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="G77" s="68"/>
       <c r="H77" s="65"/>
       <c r="I77" s="65"/>
       <c r="J77" s="65" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="K77" s="65"/>
       <c r="L77" s="65"/>
@@ -5355,23 +4745,23 @@
     </row>
     <row r="78" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A78" s="65" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="B78" s="64" t="s">
-        <v>211</v>
+        <v>201</v>
       </c>
       <c r="C78" s="64" t="s">
-        <v>212</v>
+        <v>202</v>
       </c>
       <c r="D78" s="65"/>
       <c r="E78" s="65"/>
       <c r="F78" s="65"/>
       <c r="G78" s="68"/>
       <c r="H78" s="65" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="I78" s="65" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="J78" s="65"/>
       <c r="K78" s="65"/>
@@ -5383,31 +4773,31 @@
         <v>503</v>
       </c>
       <c r="B79" s="64" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="C79" s="64" t="s">
-        <v>214</v>
+        <v>204</v>
       </c>
       <c r="D79" s="65"/>
       <c r="E79" s="66" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="F79" s="66" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="G79" s="67"/>
       <c r="H79" s="66" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="I79" s="66" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="J79" s="66"/>
       <c r="K79" s="66" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="L79" s="66" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="M79" s="66"/>
     </row>
@@ -5416,10 +4806,10 @@
         <v>503.1</v>
       </c>
       <c r="B80" s="64" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="C80" s="64" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="D80" s="65"/>
       <c r="E80" s="66"/>
@@ -5437,15 +4827,15 @@
         <v>503.2</v>
       </c>
       <c r="B81" s="64" t="s">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="C81" s="64" t="s">
-        <v>216</v>
+        <v>206</v>
       </c>
       <c r="D81" s="65"/>
       <c r="E81" s="65"/>
       <c r="F81" s="65" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="G81" s="68"/>
       <c r="H81" s="65"/>
@@ -5460,14 +4850,14 @@
         <v>503.3</v>
       </c>
       <c r="B82" s="64" t="s">
-        <v>217</v>
+        <v>207</v>
       </c>
       <c r="C82" s="64" t="s">
-        <v>218</v>
+        <v>208</v>
       </c>
       <c r="D82" s="65"/>
       <c r="E82" s="65" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="F82" s="65"/>
       <c r="G82" s="68"/>
@@ -5475,10 +4865,10 @@
       <c r="I82" s="65"/>
       <c r="J82" s="65"/>
       <c r="K82" s="65" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="L82" s="65" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="M82" s="65"/>
     </row>
@@ -5487,22 +4877,22 @@
         <v>503.4</v>
       </c>
       <c r="B83" s="64" t="s">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="C83" s="64" t="s">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="D83" s="65"/>
       <c r="E83" s="65" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="F83" s="65"/>
       <c r="G83" s="68"/>
       <c r="H83" s="65" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="I83" s="65" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="J83" s="65"/>
       <c r="K83" s="65"/>
@@ -5514,24 +4904,24 @@
         <v>504</v>
       </c>
       <c r="B84" s="64" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="C84" s="64" t="s">
-        <v>222</v>
+        <v>212</v>
       </c>
       <c r="D84" s="65"/>
       <c r="E84" s="66" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="F84" s="66" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="G84" s="67"/>
       <c r="H84" s="66" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="I84" s="66" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="J84" s="66"/>
       <c r="K84" s="66"/>
@@ -5543,10 +4933,10 @@
         <v>504.1</v>
       </c>
       <c r="B85" s="64" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="C85" s="64" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="D85" s="65"/>
       <c r="E85" s="66"/>
@@ -5564,24 +4954,24 @@
         <v>504.2</v>
       </c>
       <c r="B86" s="64" t="s">
-        <v>223</v>
+        <v>213</v>
       </c>
       <c r="C86" s="64" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="D86" s="65"/>
       <c r="E86" s="65" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="F86" s="65" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="G86" s="68"/>
       <c r="H86" s="65" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="I86" s="65" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="J86" s="65"/>
       <c r="K86" s="65"/>
@@ -5590,25 +4980,25 @@
     </row>
     <row r="87" spans="1:13" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A87" s="65" t="s">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="B87" s="64" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="C87" s="64" t="s">
-        <v>227</v>
+        <v>217</v>
       </c>
       <c r="D87" s="65"/>
       <c r="E87" s="65" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="F87" s="65"/>
       <c r="G87" s="68"/>
       <c r="H87" s="65" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="I87" s="65" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="J87" s="65"/>
       <c r="K87" s="65"/>
@@ -5617,20 +5007,20 @@
     </row>
     <row r="88" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A88" s="65" t="s">
-        <v>228</v>
+        <v>218</v>
       </c>
       <c r="B88" s="64" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
       <c r="C88" s="64" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="D88" s="65"/>
       <c r="E88" s="65" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="F88" s="65" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="G88" s="68"/>
       <c r="H88" s="65"/>
@@ -5645,24 +5035,24 @@
         <v>504.3</v>
       </c>
       <c r="B89" s="64" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="C89" s="64" t="s">
-        <v>232</v>
+        <v>222</v>
       </c>
       <c r="D89" s="65"/>
       <c r="E89" s="65" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="F89" s="65" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="G89" s="68"/>
       <c r="H89" s="65" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="I89" s="65" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="J89" s="65"/>
       <c r="K89" s="65"/>
@@ -5674,24 +5064,24 @@
         <v>504.4</v>
       </c>
       <c r="B90" s="64" t="s">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="C90" s="64" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="D90" s="65"/>
       <c r="E90" s="65" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="F90" s="65" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="G90" s="68"/>
       <c r="H90" s="65" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="I90" s="65" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="J90" s="65"/>
       <c r="K90" s="65"/>
@@ -5865,7 +5255,7 @@
     <mergeCell ref="I2:I3"/>
     <mergeCell ref="J2:J3"/>
   </mergeCells>
-  <phoneticPr fontId="4"/>
+  <phoneticPr fontId="3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
